--- a/MATH/M04/bus123-math-m04-l01-starter.xlsx
+++ b/MATH/M04/bus123-math-m04-l01-starter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS123-Solving-Business-Problems-with-Technology/MATH/M04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A630F8-5A7A-8146-9225-FA6505440A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7511C1-EA32-B548-83CD-CA33E6A2DBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6680" yWindow="920" windowWidth="29640" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1439,7 +1439,7 @@
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
     </row>
-    <row r="19" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
         <v>22</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>23</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="144" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
         <v>24</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="176" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="208" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>

--- a/MATH/M04/bus123-math-m04-l01-starter.xlsx
+++ b/MATH/M04/bus123-math-m04-l01-starter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS123-Solving-Business-Problems-with-Technology/MATH/M04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7511C1-EA32-B548-83CD-CA33E6A2DBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBBB62F-0977-7943-AB52-58C001B5A59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6680" yWindow="920" windowWidth="29640" windowHeight="20040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="START HERE" sheetId="1" r:id="rId1"/>
@@ -590,18 +590,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -609,12 +597,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -686,14 +668,32 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1000,6 +1000,9 @@
   <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
 </wetp:taskpanes>
 </file>
 
@@ -1010,6 +1013,20 @@
     <we:reference id="wa200010215" version="2.0.0.0" store="en-US" storeType="OMEX"/>
   </we:alternateReferences>
   <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{A296C07F-A15A-7442-BE23-457EC7D4228E}">
+  <we:reference id="wa200010725" version="1.0.0.1" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;06264302-e4b0-4f00-b9c7-b0d4e06fffc9&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -1031,22 +1048,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
@@ -1056,13 +1073,13 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -1072,49 +1089,49 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -1124,46 +1141,46 @@
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+      <c r="A14" s="31">
         <v>1</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1194,377 +1211,377 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="12"/>
+      <c r="D7" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="17" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="17" t="s">
+      <c r="C9" s="14"/>
+      <c r="D9" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="17" t="s">
+      <c r="C10" s="14"/>
+      <c r="D10" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="17" t="s">
+      <c r="C11" s="15"/>
+      <c r="D11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="17" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="11" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="17" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="11" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="17" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="17" t="s">
+      <c r="C17" s="16"/>
+      <c r="D17" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="17" t="s">
+      <c r="C19" s="13"/>
+      <c r="D19" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="17" t="s">
+      <c r="C20" s="13"/>
+      <c r="D20" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="17" t="s">
+      <c r="C21" s="13"/>
+      <c r="D21" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="17" t="s">
+      <c r="C22" s="16"/>
+      <c r="D22" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="17" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="176" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
+    <row r="24" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="17" t="s">
+      <c r="C24" s="16"/>
+      <c r="D24" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-    </row>
-    <row r="26" spans="1:5" ht="176" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
+      <c r="B25" s="10"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="17" t="s">
+      <c r="C26" s="13"/>
+      <c r="D26" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="272" x14ac:dyDescent="0.2">
-      <c r="A27" s="24" t="s">
+    <row r="27" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="24" t="s">
+      <c r="C27" s="19"/>
+      <c r="D27" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="E27" s="20" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1587,46 +1604,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="21" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="160" x14ac:dyDescent="0.2">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="24" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="176" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="24" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="192" x14ac:dyDescent="0.2">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="27" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1649,68 +1666,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:3" ht="192" x14ac:dyDescent="0.2">
+      <c r="A3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:3" ht="176" x14ac:dyDescent="0.2">
+      <c r="A4" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A5" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
+    <row r="6" spans="1:3" ht="208" x14ac:dyDescent="0.2">
+      <c r="A6" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>43</v>
       </c>
     </row>

--- a/MATH/M04/bus123-math-m04-l01-starter.xlsx
+++ b/MATH/M04/bus123-math-m04-l01-starter.xlsx
@@ -2,10 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
@@ -13,7 +9,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -24,53 +19,68 @@
     <numFmt numFmtId="165" formatCode="$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Aptos Display"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="004A5567"/>
+      <color rgb="FF4A5567"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="004A7C5E"/>
+      <color rgb="FF4A7C5E"/>
     </font>
     <font>
       <name val="Consolas"/>
       <b val="1"/>
-      <color rgb="00355773"/>
+      <color rgb="FF355773"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFB8843D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1A1F2C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF355773"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -79,98 +89,141 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E1116"/>
+        <fgColor rgb="FF0E1116"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+        <fgColor rgb="FFFAF8F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2EEE5"/>
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00355773"/>
+        <fgColor rgb="FF355773"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C4"/>
+        <fgColor rgb="FFFFF3C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCEBFF"/>
+        <fgColor rgb="FFDCEBFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EC"/>
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="9">
+    <border/>
     <border>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
     <border>
-      <right/>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00B8843D"/>
-      </left>
-      <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="004A7C5E"/>
+        <color rgb="FFB8843D"/>
       </left>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4A7C5E"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E1D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -233,11 +286,67 @@
     <xf numFmtId="166" fontId="4" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -310,7 +419,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -352,72 +461,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -473,7 +524,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -482,13 +533,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -522,17 +573,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -587,8 +627,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -610,25 +648,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Anchor &amp; Oak Pricing Lab</t>
         </is>
       </c>
+      <c r="B1" s="46" t="n"/>
+      <c r="C1" s="46" t="n"/>
+      <c r="D1" s="46" t="n"/>
+      <c r="E1" s="46" t="n"/>
+      <c r="F1" s="46" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>BUS123 MATH M04 L01 - Markups, Markdowns, and Break-Even</t>
         </is>
       </c>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>Live You Try It is self-graded with hints and feedback. Class Challenge is the graded or next-level activity.</t>
         </is>
       </c>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -652,7 +705,7 @@
           <t>What to do first</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="49" t="inlineStr">
         <is>
           <t>Open the Live You Try It tab during the slide pauses. Use the exact numbers from the worked examples.</t>
         </is>
@@ -668,7 +721,7 @@
           <t>Self-grade live practice</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="49" t="inlineStr">
         <is>
           <t>Use the hint and feedback cells to check your formula logic before moving on.</t>
         </is>
@@ -684,7 +737,7 @@
           <t>Then level up</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="49" t="inlineStr">
         <is>
           <t>Use the Class Challenge tab for harder scenarios that combine markup, markdown, and break-even.</t>
         </is>
@@ -700,7 +753,7 @@
           <t>Remember</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="49" t="inlineStr">
         <is>
           <t>Name the base first: cost, original selling price, or contribution margin.</t>
         </is>
@@ -728,7 +781,7 @@
           <t>I can</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>Calculate markup based on cost and selling price.</t>
         </is>
@@ -744,7 +797,7 @@
           <t>I can</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>Calculate markdowns from original selling price.</t>
         </is>
@@ -760,7 +813,7 @@
           <t>I can</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
         <is>
           <t>Use contribution margin to estimate break-even units.</t>
         </is>
@@ -776,7 +829,7 @@
           <t>I can</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>Explain how pricing assumptions affect an event decision.</t>
         </is>
@@ -800,7 +853,7 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -822,25 +875,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Live You Try It</t>
         </is>
       </c>
+      <c r="B1" s="46" t="n"/>
+      <c r="C1" s="46" t="n"/>
+      <c r="D1" s="46" t="n"/>
+      <c r="E1" s="46" t="n"/>
+      <c r="F1" s="46" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Self-graded practice using the exact numbers from the slides</t>
         </is>
       </c>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>Enter yellow inputs, build blue formulas, then read the green feedback. These cells are for learning, not private grading.</t>
         </is>
       </c>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -1134,7 +1202,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1156,25 +1224,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Class Challenge</t>
         </is>
       </c>
+      <c r="B1" s="46" t="n"/>
+      <c r="C1" s="46" t="n"/>
+      <c r="D1" s="46" t="n"/>
+      <c r="E1" s="46" t="n"/>
+      <c r="F1" s="46" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr">
         <is>
           <t>Next-level pricing scenarios for Anchor &amp; Oak Events</t>
         </is>
       </c>
+      <c r="B2" s="46" t="n"/>
+      <c r="C2" s="46" t="n"/>
+      <c r="D2" s="46" t="n"/>
+      <c r="E2" s="46" t="n"/>
+      <c r="F2" s="46" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>These formulas combine ideas from the lesson. Use the Live You Try It tab as a model, then explain the business meaning in your own words.</t>
         </is>
       </c>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1619,7 +1702,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1632,156 +1715,150 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21.11000061035156" customWidth="1" min="1" max="1"/>
+    <col width="25.55999946594238" customWidth="1" min="2" max="2"/>
+    <col width="34.43999862670898" customWidth="1" min="3" max="3"/>
+    <col width="33.33000183105469" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Formula Reference Card</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Use these patterns after you choose the correct base</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="1" ht="31.5" customHeight="1">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>Concept</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B1" s="37" t="inlineStr">
         <is>
           <t>Excel Pattern</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C1" s="37" t="inlineStr">
         <is>
           <t>Plain-English Meaning</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr"/>
-      <c r="E4" s="11" t="inlineStr"/>
-      <c r="F4" s="11" t="inlineStr"/>
-    </row>
-    <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D1" s="37" t="inlineStr">
+        <is>
+          <t>Watch Out For</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="31.5" customHeight="1">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>Markup on cost</t>
         </is>
       </c>
-      <c r="B5" s="21">
-        <f>Cost*(1+MarkupRate)</f>
-        <v/>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Cost plus a percentage of cost</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>=Cost*(1+MarkupRate)</t>
+        </is>
+      </c>
+      <c r="C2" s="41" t="inlineStr">
+        <is>
+          <t>Cost plus a percentage of cost.</t>
+        </is>
+      </c>
+      <c r="D2" s="44" t="inlineStr">
+        <is>
+          <t>The base is cost, not selling price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Markdown</t>
         </is>
       </c>
-      <c r="B6" s="21">
-        <f>OriginalPrice*(1-MarkdownRate)</f>
-        <v/>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Price after a reduction</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>=OriginalPrice*(1-MarkdownRate)</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>Price after a reduction.</t>
+        </is>
+      </c>
+      <c r="D3" s="44" t="inlineStr">
+        <is>
+          <t>Subtract the markdown rate from 1 first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>Contribution margin</t>
         </is>
       </c>
-      <c r="B7" s="21">
-        <f>SellingPrice-VariableCost</f>
-        <v/>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Amount each unit contributes before fixed costs</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
+        <is>
+          <t>=SellingPrice-VariableCost</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Amount each unit contributes before fixed costs.</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>Use per-unit values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>Break-even units</t>
         </is>
       </c>
-      <c r="B8" s="21">
-        <f>ROUNDUP(FixedCosts/ContributionMargin,0)</f>
-        <v/>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Whole units needed to cover fixed costs</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>=ROUNDUP(FixedCosts/ContributionMargin,0)</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Whole units needed to cover fixed costs.</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>Round up because partial units do not cover costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Target-profit units</t>
         </is>
       </c>
-      <c r="B9" s="21">
-        <f>ROUNDUP((FixedCosts+TargetProfit)/ContributionMargin,0)</f>
-        <v/>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Whole units needed to cover fixed costs and target profit</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-    </row>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>=ROUNDUP((FixedCosts+TargetProfit)/ContributionMargin,0)</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>Whole units needed to cover fixed costs and target profit.</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>Add target profit before dividing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1"/>
+    <row r="8" ht="36" customHeight="1"/>
+    <row r="9" ht="36" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/MATH/M04/bus123-math-m04-l01-starter.xlsx
+++ b/MATH/M04/bus123-math-m04-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R7af9b6c84c2c4ef1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="Rc86a44164caf44a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R79a4582894a64164"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R521c3346877341ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R190916d5a17d43a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R44a29987f8c143d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rb08c25afeb2f43cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Ra1fa30031cce4367"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,12 +16,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="$#,##0"/>
     <x:numFmt numFmtId="166" formatCode="0.0%"/>
+    <x:numFmt numFmtId="200" formatCode="0%"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="23">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -81,8 +83,77 @@
       <x:color rgb="FF355773"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="20"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0E1116"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="JetBrains Mono"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF4A7C5E"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C4A2B"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0E1116"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF4A5567"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF4A5567"/>
+      <x:name val="DM Sans"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="JetBrains Mono"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0E1116"/>
+      <x:name val="DM Sans"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -164,8 +235,93 @@
         <x:fgColor rgb="FFF2EEE5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFAF8F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="10">
     <x:border/>
     <x:border>
       <x:top style="thin">
@@ -221,11 +377,25 @@
         <x:color rgb="FFE5E1D6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D3C5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D3C5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D3C5"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D3C5"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="209">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -344,6 +514,424 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="4" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="13" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="4" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="4" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="14" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="4" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="4" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="23" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="24" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="24" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="26" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="27" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="27" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="14" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="27" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="25" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="29" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="29" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="29" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="4" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="4" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="4" fillId="29" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="29" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="30" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="30" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="32" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="32" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="14" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="31" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -644,17 +1232,17 @@
     <x:col min="6" max="6" width="34" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="45" t="inlineStr">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="174" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Anchor &amp; Oak Pricing Lab</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="46" t="n"/>
-      <x:c r="C1" s="46" t="n"/>
-      <x:c r="D1" s="46" t="n"/>
-      <x:c r="E1" s="46" t="n"/>
-      <x:c r="F1" s="46" t="n"/>
+      <x:c r="B1" s="175" t="n"/>
+      <x:c r="C1" s="175" t="n"/>
+      <x:c r="D1" s="175" t="n"/>
+      <x:c r="E1" s="175" t="n"/>
+      <x:c r="F1" s="175" t="n"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="47" t="inlineStr">
@@ -874,25 +1462,25 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="24" customWidth="1"/>
-    <x:col min="2" max="2" width="42" customWidth="1"/>
-    <x:col min="3" max="3" width="18" customWidth="1"/>
-    <x:col min="4" max="4" width="22" customWidth="1"/>
-    <x:col min="5" max="5" width="34" customWidth="1"/>
-    <x:col min="6" max="6" width="34" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="45" t="inlineStr">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="174" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Live You Try It</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="46" t="n"/>
-      <x:c r="C1" s="46" t="n"/>
-      <x:c r="D1" s="46" t="n"/>
-      <x:c r="E1" s="46" t="n"/>
-      <x:c r="F1" s="46" t="n"/>
+      <x:c r="B1" s="175" t="n"/>
+      <x:c r="C1" s="175" t="n"/>
+      <x:c r="D1" s="175" t="n"/>
+      <x:c r="E1" s="175" t="n"/>
+      <x:c r="F1" s="175" t="n"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="47" t="inlineStr">
@@ -918,289 +1506,285 @@
       <x:c r="E3" s="46" t="n"/>
       <x:c r="F3" s="46" t="n"/>
     </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="11" t="inlineStr">
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="184" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Pause</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="11" t="inlineStr">
+      <x:c r="B4" s="184" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">What to model</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input / Formula</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Your result</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="11" t="inlineStr">
+      <x:c r="C4" s="184" t="str">
+        <x:v>Given input</x:v>
+      </x:c>
+      <x:c r="D4" s="184" t="str">
+        <x:v>Your formula / result</x:v>
+      </x:c>
+      <x:c r="E4" s="184" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Hint</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="11" t="inlineStr">
+      <x:c r="F4" s="184" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Feedback</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
-      <x:c r="A5" s="6" t="inlineStr">
+    <x:row r="5" ht="52" customHeight="1">
+      <x:c r="A5" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markup</x:t>
         </x:is>
       </x:c>
-      <x:c r="B5" s="6" t="inlineStr">
+      <x:c r="B5" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cost from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C5" s="12" t="n">
+      <x:c r="C5" s="185" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D5" s="6" t="n"/>
-      <x:c r="E5" s="6" t="str">
+      <x:c r="D5" s="177" t="n"/>
+      <x:c r="E5" s="84" t="str">
         <x:v>Use the tasting box cost from the worked example.</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="n"/>
-    </x:row>
-    <x:row r="6" ht="36" customHeight="1">
-      <x:c r="A6" s="6" t="inlineStr">
+      <x:c r="F5" s="84" t="n"/>
+    </x:row>
+    <x:row r="6" ht="52" customHeight="1">
+      <x:c r="A6" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markup</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="6" t="inlineStr">
+      <x:c r="B6" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markup rate from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" s="13" t="n">
+      <x:c r="C6" s="186" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="n"/>
-      <x:c r="E6" s="6" t="inlineStr">
+      <x:c r="D6" s="177" t="n"/>
+      <x:c r="E6" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Enter 45% as a percent.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="6" t="n"/>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1">
-      <x:c r="A7" s="6" t="inlineStr">
+      <x:c r="F6" s="84" t="n"/>
+    </x:row>
+    <x:row r="7" ht="52" customHeight="1">
+      <x:c r="A7" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markup</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="6" t="inlineStr">
+      <x:c r="B7" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Selling price</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" s="6" t="n"/>
-      <x:c r="D7" s="14" t="n"/>
-      <x:c r="E7" s="6" t="inlineStr">
+      <x:c r="C7" s="177" t="n"/>
+      <x:c r="D7" s="187"/>
+      <x:c r="E7" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cost x (1 + Markup Rate)</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="15" t="str">
+      <x:c r="F7" s="88" t="str">
         <x:f>IF(ABS(D7-26.1)&lt;0.01,"Correct: markup builds from $18.00 to $26.10.","Check the base: use cost, then multiply by 1 + markup rate.")</x:f>
         <x:v>Check the base: use cost, then multiply by 1 + markup rate.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="36" customHeight="1">
-      <x:c r="A8" s="6" t="inlineStr">
+    <x:row r="8" ht="52" customHeight="1">
+      <x:c r="A8" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markdown</x:t>
         </x:is>
       </x:c>
-      <x:c r="B8" s="6" t="inlineStr">
+      <x:c r="B8" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Original price from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" s="6" t="n">
+      <x:c r="C8" s="185" t="n">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="n"/>
-      <x:c r="E8" s="6" t="inlineStr">
+      <x:c r="D8" s="177" t="n"/>
+      <x:c r="E8" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Use the original selling price before the discount.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="6" t="n"/>
-    </x:row>
-    <x:row r="9" ht="36" customHeight="1">
-      <x:c r="A9" s="6" t="inlineStr">
+      <x:c r="F8" s="84" t="n"/>
+    </x:row>
+    <x:row r="9" ht="52" customHeight="1">
+      <x:c r="A9" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markdown</x:t>
         </x:is>
       </x:c>
-      <x:c r="B9" s="6" t="inlineStr">
+      <x:c r="B9" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markdown rate from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" s="12" t="n">
+      <x:c r="C9" s="186" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="n"/>
-      <x:c r="E9" s="6" t="inlineStr">
+      <x:c r="D9" s="177" t="n"/>
+      <x:c r="E9" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Enter 20% as a percent.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F9" s="6" t="n"/>
-    </x:row>
-    <x:row r="10" ht="36" customHeight="1">
-      <x:c r="A10" s="6" t="inlineStr">
+      <x:c r="F9" s="84" t="n"/>
+    </x:row>
+    <x:row r="10" ht="52" customHeight="1">
+      <x:c r="A10" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Markdown</x:t>
         </x:is>
       </x:c>
-      <x:c r="B10" s="6" t="inlineStr">
+      <x:c r="B10" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Sale price</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" s="13" t="n"/>
-      <x:c r="D10" s="6" t="n"/>
-      <x:c r="E10" s="6" t="inlineStr">
+      <x:c r="C10" s="180" t="n"/>
+      <x:c r="D10" s="187"/>
+      <x:c r="E10" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Original Price x (1 - Markdown Rate)</x:t>
         </x:is>
       </x:c>
-      <x:c r="F10" s="6" t="str">
+      <x:c r="F10" s="84" t="str">
         <x:f>IF(ABS(D10-41.6)&lt;0.01,"Correct: the markdown price is $41.60.","Check the base: markdown starts from original price, not cost.")</x:f>
         <x:v>Check the base: markdown starts from original price, not cost.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="36" customHeight="1">
-      <x:c r="A11" s="6" t="inlineStr">
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Break-even</x:t>
         </x:is>
       </x:c>
-      <x:c r="B11" s="6" t="inlineStr">
+      <x:c r="B11" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fixed costs from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" s="6" t="n">
+      <x:c r="C11" s="185" t="n">
         <x:v>3600</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="n"/>
-      <x:c r="E11" s="6" t="inlineStr">
+      <x:c r="D11" s="181" t="n"/>
+      <x:c r="E11" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fixed costs stay the same across guests.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" s="15" t="n"/>
-    </x:row>
-    <x:row r="12" ht="36" customHeight="1">
-      <x:c r="A12" s="6" t="inlineStr">
+      <x:c r="F11" s="88" t="n"/>
+    </x:row>
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Break-even</x:t>
         </x:is>
       </x:c>
-      <x:c r="B12" s="6" t="inlineStr">
+      <x:c r="B12" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Selling price from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="6" t="n">
+      <x:c r="C12" s="185" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="n"/>
-      <x:c r="E12" s="6" t="inlineStr">
+      <x:c r="D12" s="177" t="n"/>
+      <x:c r="E12" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Ticket price per guest.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="6" t="n"/>
-    </x:row>
-    <x:row r="13" ht="36" customHeight="1">
-      <x:c r="A13" s="6" t="inlineStr">
+      <x:c r="F12" s="84" t="n"/>
+    </x:row>
+    <x:row r="13" ht="52" customHeight="1">
+      <x:c r="A13" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Break-even</x:t>
         </x:is>
       </x:c>
-      <x:c r="B13" s="6" t="inlineStr">
+      <x:c r="B13" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Variable cost from slide</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="16" t="n">
+      <x:c r="C13" s="185" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="n"/>
-      <x:c r="E13" s="6" t="inlineStr">
+      <x:c r="D13" s="177" t="n"/>
+      <x:c r="E13" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cost that moves with each guest.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F13" s="6" t="n"/>
-    </x:row>
-    <x:row r="14" ht="36" customHeight="1">
-      <x:c r="A14" s="6" t="inlineStr">
+      <x:c r="F13" s="84" t="n"/>
+    </x:row>
+    <x:row r="14" ht="52" customHeight="1">
+      <x:c r="A14" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Break-even</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="6" t="inlineStr">
+      <x:c r="B14" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Contribution margin</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="16" t="n"/>
-      <x:c r="D14" s="6" t="n"/>
-      <x:c r="E14" s="6" t="inlineStr">
+      <x:c r="C14" s="182" t="n"/>
+      <x:c r="D14" s="187"/>
+      <x:c r="E14" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Selling price - variable cost</x:t>
         </x:is>
       </x:c>
-      <x:c r="F14" s="6" t="str">
+      <x:c r="F14" s="84" t="str">
         <x:f>IF(ABS(D14-21)&lt;0.01,"Correct: each guest contributes $21 before fixed costs.","Calculate contribution margin before break-even.")</x:f>
         <x:v>Calculate contribution margin before break-even.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="36" customHeight="1">
-      <x:c r="A15" s="6" t="inlineStr">
+    <x:row r="15" ht="52" customHeight="1">
+      <x:c r="A15" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Break-even</x:t>
         </x:is>
       </x:c>
-      <x:c r="B15" s="6" t="inlineStr">
+      <x:c r="B15" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Break-even guests</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" s="16" t="n"/>
-      <x:c r="D15" s="6" t="n"/>
-      <x:c r="E15" s="6" t="inlineStr">
+      <x:c r="C15" s="182" t="n"/>
+      <x:c r="D15" s="188"/>
+      <x:c r="E15" s="84" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Fixed costs ÷ contribution margin; round up.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F15" s="6" t="str">
+      <x:c r="F15" s="84" t="str">
         <x:f>IF(D15=172,"Correct: Anchor &amp; Oak needs 172 guests to break even.","Round up because the event cannot sell part of a guest.")</x:f>
         <x:v>Round up because the event cannot sell part of a guest.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="D16" s="17" t="n"/>
-      <x:c r="F16" s="18" t="n"/>
+      <x:c r="D16"/>
+      <x:c r="F16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="D17" s="19" t="n"/>
-      <x:c r="F17" s="18" t="n"/>
+      <x:c r="D17"/>
+      <x:c r="F17"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1216,25 +1800,25 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" customWidth="1"/>
-    <x:col min="2" max="2" width="46" customWidth="1"/>
-    <x:col min="3" max="3" width="30" customWidth="1"/>
-    <x:col min="4" max="4" width="18" customWidth="1"/>
-    <x:col min="5" max="5" width="38" customWidth="1"/>
-    <x:col min="6" max="6" width="30" customWidth="1"/>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="45" t="inlineStr">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="174" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Class Challenge</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="46" t="n"/>
-      <x:c r="C1" s="46" t="n"/>
-      <x:c r="D1" s="46" t="n"/>
-      <x:c r="E1" s="46" t="n"/>
-      <x:c r="F1" s="46" t="n"/>
+      <x:c r="B1" s="175" t="n"/>
+      <x:c r="C1" s="175" t="n"/>
+      <x:c r="D1" s="175" t="n"/>
+      <x:c r="E1" s="175" t="n"/>
+      <x:c r="F1" s="175" t="n"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="47" t="inlineStr">
@@ -1261,441 +1845,216 @@
       <x:c r="F3" s="46" t="n"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scenario</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Given facts</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula to build</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Your answer</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Explain the business meaning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Instructor check</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Waste-adjusted package price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use $18 cost, 45% markup, 120 produced packages, and 15% expected waste.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Required price per sellable package</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="14" t="n"/>
-      <x:c r="E5" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why is this price higher than $26.10?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="15" t="e">
-        <x:f>IF(ISFORMULA(D5),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Discounted break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the $52 original price, 20% markdown, $3,600 fixed cost, and $27 variable cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guests needed after the markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="20" t="n"/>
-      <x:c r="E6" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What risk does the discount create?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="15" t="e">
-        <x:f>IF(ISFORMULA(D6),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Profit target at regular price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use $3,600 fixed cost, $48 ticket price, $27 variable cost, and a $1,500 profit target.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guests needed for target profit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="20" t="n"/>
-      <x:c r="E7" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">How is this different from break-even?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="15" t="e">
-        <x:f>IF(ISFORMULA(D7),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Profit target after markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use the $41.60 markdown price, $3,600 fixed cost, $27 variable cost, and a $1,500 profit target.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guests needed after discount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="20" t="n"/>
-      <x:c r="E8" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Would you recommend the discount? Why?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="15" t="e">
-        <x:f>IF(ISFORMULA(D8),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Regular contribution margin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ticket price is $48 and variable cost is $27 per guest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contribution margin per guest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="14" t="n"/>
-      <x:c r="E9" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What does this number help pay for?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="15" t="e">
-        <x:f>IF(ISFORMULA(D9),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown contribution margin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Original price is $52, markdown is 20%, and variable cost is $27 per guest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contribution margin after markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="14" t="n"/>
-      <x:c r="E10" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why is this lower than the regular contribution margin?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="15" t="e">
-        <x:f>IF(ISFORMULA(D10),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guest cushion above break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use 200 expected guests, $3,600 fixed cost, $48 ticket price, and $27 variable cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Guests above break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="20" t="n"/>
-      <x:c r="E11" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What does the cushion tell Anchor &amp; Oak?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="15" t="e">
-        <x:f>IF(ISFORMULA(D11),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Regular-price profit at 200 guests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use 200 guests, $48 ticket price, $27 variable cost, and $3,600 fixed cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Projected profit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="14" t="n"/>
-      <x:c r="E12" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Is the event past break-even?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="15" t="e">
-        <x:f>IF(ISFORMULA(D12),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="A4" s="189" t="str">
+        <x:v>Scenario</x:v>
+      </x:c>
+      <x:c r="B4" s="189" t="str">
+        <x:v>Business question</x:v>
+      </x:c>
+      <x:c r="C4" s="189" t="str">
+        <x:v>Given inputs</x:v>
+      </x:c>
+      <x:c r="D4" s="189" t="str">
+        <x:v>Your formula / result</x:v>
+      </x:c>
+      <x:c r="E4" s="189" t="str">
+        <x:v>Decision note</x:v>
+      </x:c>
+      <x:c r="F4" s="189" t="str">
+        <x:v>Formula check</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="52" customHeight="1">
+      <x:c r="A5" s="190" t="str">
+        <x:v>Required 1</x:v>
+      </x:c>
+      <x:c r="B5" s="191" t="str">
+        <x:v>Find the waste-adjusted package price</x:v>
+      </x:c>
+      <x:c r="C5" s="191" t="str">
+        <x:v>120 produced; $18 cost; 45% markup; 15% waste</x:v>
+      </x:c>
+      <x:c r="D5" s="187"/>
+      <x:c r="E5" s="195"/>
+      <x:c r="F5" s="196" t="str">
+        <x:f>IF(D5="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="52" customHeight="1">
+      <x:c r="A6" s="190" t="str">
+        <x:v>Required 2</x:v>
+      </x:c>
+      <x:c r="B6" s="191" t="str">
+        <x:v>Find break-even after a 10% ticket markdown</x:v>
+      </x:c>
+      <x:c r="C6" s="191" t="str">
+        <x:v>$48 ticket; 10% markdown; $27 VC; $3,600 FC</x:v>
+      </x:c>
+      <x:c r="D6" s="194"/>
+      <x:c r="E6" s="195"/>
+      <x:c r="F6" s="196" t="str">
+        <x:f>IF(D6="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="52" customHeight="1">
+      <x:c r="A7" s="190" t="str">
+        <x:v>Required 3</x:v>
+      </x:c>
+      <x:c r="B7" s="191" t="str">
+        <x:v>Find units for a $1,200 profit target after markdown</x:v>
+      </x:c>
+      <x:c r="C7" s="191" t="str">
+        <x:v>$52 price; 20% markdown; $24 VC; $2,500 FC</x:v>
+      </x:c>
+      <x:c r="D7" s="194"/>
+      <x:c r="E7" s="195"/>
+      <x:c r="F7" s="196" t="str">
+        <x:f>IF(D7="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="52" customHeight="1">
+      <x:c r="A8" s="190" t="str">
+        <x:v>Required 4</x:v>
+      </x:c>
+      <x:c r="B8" s="191" t="str">
+        <x:v>Find profit at 200 regular-price guests</x:v>
+      </x:c>
+      <x:c r="C8" s="191" t="str">
+        <x:v>$48 price; $27 VC; $3,600 FC; 200 guests</x:v>
+      </x:c>
+      <x:c r="D8" s="194"/>
+      <x:c r="E8" s="195"/>
+      <x:c r="F8" s="196" t="str">
+        <x:f>IF(D8="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="52" customHeight="1">
+      <x:c r="A9" s="192" t="str">
+        <x:v>Extension 1</x:v>
+      </x:c>
+      <x:c r="B9" s="193" t="str">
+        <x:v>Find regular-price contribution margin</x:v>
+      </x:c>
+      <x:c r="C9" s="193" t="str">
+        <x:v>$48 price; $27 variable cost</x:v>
+      </x:c>
+      <x:c r="D9" s="187"/>
+      <x:c r="E9" s="195"/>
+      <x:c r="F9" s="196" t="str">
+        <x:f>IF(D9="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="52" customHeight="1">
+      <x:c r="A10" s="192" t="str">
+        <x:v>Extension 2</x:v>
+      </x:c>
+      <x:c r="B10" s="193" t="str">
+        <x:v>Find markup on cost needed for a $30 price</x:v>
+      </x:c>
+      <x:c r="C10" s="193" t="str">
+        <x:v>$18 cost; $30 selling price</x:v>
+      </x:c>
+      <x:c r="D10" s="187"/>
+      <x:c r="E10" s="195"/>
+      <x:c r="F10" s="196" t="str">
+        <x:f>IF(D10="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="52" customHeight="1">
+      <x:c r="A11" s="192" t="str">
+        <x:v>Extension 3</x:v>
+      </x:c>
+      <x:c r="B11" s="193" t="str">
+        <x:v>Find the minimum ticket price for 150 guests</x:v>
+      </x:c>
+      <x:c r="C11" s="193" t="str">
+        <x:v>$3,600 FC; $27 VC; 150 guests</x:v>
+      </x:c>
+      <x:c r="D11" s="194"/>
+      <x:c r="E11" s="195"/>
+      <x:c r="F11" s="196" t="str">
+        <x:f>IF(D11="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="192" t="str">
+        <x:v>Extension 4</x:v>
+      </x:c>
+      <x:c r="B12" s="193" t="str">
+        <x:v>Find extra guests needed for $1,000 more profit</x:v>
+      </x:c>
+      <x:c r="C12" s="193" t="str">
+        <x:v>$21 contribution margin; $1,000 target</x:v>
+      </x:c>
+      <x:c r="D12" s="187"/>
+      <x:c r="E12" s="195"/>
+      <x:c r="F12" s="196" t="str">
+        <x:f>IF(D12="","Build a formula","Formula entered - verify the result")</x:f>
+        <x:v>Build a formula</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown profit at 200 guests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use 200 guests, $52 original price, 20% markdown, $27 variable cost, and $3,600 fixed cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Projected profit after discount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="14" t="n"/>
-      <x:c r="E13" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Does the markdown still cover fixed cost?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="15" t="e">
-        <x:f>IF(ISFORMULA(D13),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Minimum ticket for 150 guests</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use 150 expected guests, $3,600 fixed cost, and $27 variable cost per guest.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Minimum break-even ticket price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="14" t="n"/>
-      <x:c r="E14" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why does lower attendance require a higher ticket?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="15" t="e">
-        <x:f>IF(ISFORMULA(D14),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
     </x:row>
     <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Minimum ticket for target profit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use 150 guests, $3,600 fixed cost, $27 variable cost, and $1,500 target profit.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ticket price needed for target profit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="14" t="n"/>
-      <x:c r="E15" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why is this higher than break-even price?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="15" t="e">
-        <x:f>IF(ISFORMULA(D15),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
     </x:row>
     <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup rate needed for $30 price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A package costs $18 and Anchor &amp; Oak wants to charge $30.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup rate on cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="23" t="n"/>
-      <x:c r="E16" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">How does this compare with the 45% slide markup?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="15" t="e">
-        <x:f>IF(ISFORMULA(D16),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
-      <x:c r="A17" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown dollar amount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Original price is $52 and sale price after markdown is $41.60.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dollar markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="14" t="n"/>
-      <x:c r="E17" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why should students name the original-price base?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="15" t="e">
-        <x:f>IF(ISFORMULA(D17),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
     </x:row>
     <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Revenue at break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use $3,600 fixed cost, $48 ticket price, and $27 variable cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even revenue</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="14" t="n"/>
-      <x:c r="E18" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Why is revenue different from profit?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="15" t="e">
-        <x:f>IF(ISFORMULA(D18),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
     </x:row>
     <x:row r="19" ht="48" customHeight="1">
-      <x:c r="A19" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Extra guests for target profit</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use $3,600 fixed cost, $48 ticket price, $27 variable cost, and $1,500 target profit.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Additional guests beyond break-even</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="20" t="n"/>
-      <x:c r="E19" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">What does this say about the target profit?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="15" t="e">
-        <x:f>IF(ISFORMULA(D19),"Formula present","Build this as an Excel formula")</x:f>
-        <x:v>#VALUE!</x:v>
-      </x:c>
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1711,150 +2070,161 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21.110000610351562" customWidth="1"/>
-    <x:col min="2" max="2" width="25.559999465942383" customWidth="1"/>
-    <x:col min="3" max="3" width="34.439998626708984" customWidth="1"/>
-    <x:col min="4" max="4" width="33.33000183105469" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="37" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="34" customWidth="1"/>
     <x:col min="6" max="6" width="34" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="31.5" customHeight="1">
-      <x:c r="A1" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Concept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Excel Pattern</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Plain-English Meaning</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Watch Out For</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="31.5" customHeight="1">
-      <x:c r="A2" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markup on cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">=Cost*(1+MarkupRate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cost plus a percentage of cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The base is cost, not selling price.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="31.5" customHeight="1">
-      <x:c r="A3" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Markdown</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">=OriginalPrice*(1-MarkdownRate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Price after a reduction.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Subtract the markdown rate from 1 first.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="31.5" customHeight="1">
-      <x:c r="A4" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Contribution margin</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">=SellingPrice-VariableCost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Amount each unit contributes before fixed costs.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use per-unit values.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="31.5" customHeight="1">
-      <x:c r="A5" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Break-even units</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">=ROUNDUP(FixedCosts/ContributionMargin,0)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Whole units needed to cover fixed costs.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Round up because partial units do not cover costs.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="31.5" customHeight="1">
-      <x:c r="A6" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Target-profit units</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">=ROUNDUP((FixedCosts+TargetProfit)/ContributionMargin,0)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Whole units needed to cover fixed costs and target profit.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Add target profit before dividing.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" customHeight="1"/>
-    <x:row r="8" ht="36" customHeight="1"/>
-    <x:row r="9" ht="36" customHeight="1"/>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="175" t="str">
+        <x:v>MATH M04 · Formula Reference Card</x:v>
+      </x:c>
+      <x:c r="B1" s="175"/>
+      <x:c r="C1" s="175"/>
+      <x:c r="D1" s="175"/>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="200" t="str">
+        <x:v>Name the base first, then choose the Excel pattern that matches the decision.</x:v>
+      </x:c>
+      <x:c r="B2" s="200"/>
+      <x:c r="C2" s="200"/>
+      <x:c r="D2" s="200"/>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="184" t="str">
+        <x:v>Concept</x:v>
+      </x:c>
+      <x:c r="B3" s="184" t="str">
+        <x:v>Excel pattern</x:v>
+      </x:c>
+      <x:c r="C3" s="184" t="str">
+        <x:v>Plain meaning</x:v>
+      </x:c>
+      <x:c r="D3" s="184" t="str">
+        <x:v>Watch out</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="44" customHeight="1">
+      <x:c r="A4" s="136" t="str">
+        <x:v>Markup amount</x:v>
+      </x:c>
+      <x:c r="B4" s="208" t="str">
+        <x:v>=SellingPrice-Cost</x:v>
+      </x:c>
+      <x:c r="C4" s="138" t="str">
+        <x:v>Dollar amount added above cost</x:v>
+      </x:c>
+      <x:c r="D4" s="138" t="str">
+        <x:v>This is an amount, not a rate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="44" customHeight="1">
+      <x:c r="A5" s="136" t="str">
+        <x:v>Markup on cost</x:v>
+      </x:c>
+      <x:c r="B5" s="208" t="str">
+        <x:v>=MarkupAmount/Cost</x:v>
+      </x:c>
+      <x:c r="C5" s="138" t="str">
+        <x:v>Markup measured against cost</x:v>
+      </x:c>
+      <x:c r="D5" s="138" t="str">
+        <x:v>Cost is the denominator</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="44" customHeight="1">
+      <x:c r="A6" s="136" t="str">
+        <x:v>Selling price from markup</x:v>
+      </x:c>
+      <x:c r="B6" s="208" t="str">
+        <x:v>=Cost*(1+MarkupRate)</x:v>
+      </x:c>
+      <x:c r="C6" s="138" t="str">
+        <x:v>Build a selling price up from cost</x:v>
+      </x:c>
+      <x:c r="D6" s="138" t="str">
+        <x:v>Enter 45% as 45%, not 45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="44" customHeight="1">
+      <x:c r="A7" s="136" t="str">
+        <x:v>Markdown price</x:v>
+      </x:c>
+      <x:c r="B7" s="208" t="str">
+        <x:v>=OriginalPrice*(1-MarkdownRate)</x:v>
+      </x:c>
+      <x:c r="C7" s="138" t="str">
+        <x:v>Reduce the original selling price</x:v>
+      </x:c>
+      <x:c r="D7" s="138" t="str">
+        <x:v>Original price is the base</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="44" customHeight="1">
+      <x:c r="A8" s="136" t="str">
+        <x:v>Sellable units</x:v>
+      </x:c>
+      <x:c r="B8" s="208" t="str">
+        <x:v>=ProducedUnits*(1-WasteRate)</x:v>
+      </x:c>
+      <x:c r="C8" s="138" t="str">
+        <x:v>Remove expected waste from production</x:v>
+      </x:c>
+      <x:c r="D8" s="138" t="str">
+        <x:v>Do not divide revenue by all produced units</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="44" customHeight="1">
+      <x:c r="A9" s="136" t="str">
+        <x:v>Contribution margin</x:v>
+      </x:c>
+      <x:c r="B9" s="208" t="str">
+        <x:v>=SellingPrice-VariableCost</x:v>
+      </x:c>
+      <x:c r="C9" s="138" t="str">
+        <x:v>Amount each unit contributes to fixed cost and profit</x:v>
+      </x:c>
+      <x:c r="D9" s="138" t="str">
+        <x:v>Subtract variable cost per unit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="44" customHeight="1">
+      <x:c r="A10" s="136" t="str">
+        <x:v>Break-even units</x:v>
+      </x:c>
+      <x:c r="B10" s="208" t="str">
+        <x:v>=ROUNDUP(FixedCosts/ContributionMargin,0)</x:v>
+      </x:c>
+      <x:c r="C10" s="138" t="str">
+        <x:v>Whole units required to cover fixed costs</x:v>
+      </x:c>
+      <x:c r="D10" s="138" t="str">
+        <x:v>Round up, never down</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="44" customHeight="1">
+      <x:c r="A11" s="136" t="str">
+        <x:v>Break-even revenue</x:v>
+      </x:c>
+      <x:c r="B11" s="208" t="str">
+        <x:v>=BreakEvenUnits*SellingPrice</x:v>
+      </x:c>
+      <x:c r="C11" s="138" t="str">
+        <x:v>Sales dollars at break-even volume</x:v>
+      </x:c>
+      <x:c r="D11" s="138" t="str">
+        <x:v>Use the rounded whole-unit volume</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>